--- a/pipeline/lz_spec/landing_zone_spec.xlsx
+++ b/pipeline/lz_spec/landing_zone_spec.xlsx
@@ -19248,12 +19248,12 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
     </row>
@@ -27349,7 +27349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H132"/>
+  <dimension ref="A1:H145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -27434,7 +27434,7 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Required. Delegated administrator account from 01_Foundation where the central audit resources are deployed, including the organization CTS tracker, audit bucket, KMS key, and CTS log group and stream.</t>
+          <t>Required. Delegated administrator account from 01_Foundation where the central audit resources are deployed, including the organization CTS tracker, audit bucket and KMS key. CTS writes the trail to an LTS group/stream it creates itself in this account (CTS / system-trace).</t>
         </is>
       </c>
       <c r="F6" s="10" t="n"/>
@@ -27498,27 +27498,23 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>lts_hot_retention_days</t>
+          <t>audit_bucket_name</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr"/>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>{account-name}-sg-prd-ldz-audit-01</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Hot retention period for the CTS LTS log stream.</t>
+          <t>Required. Globally unique CTS audit OBS bucket name. Supports the {account-name} token.</t>
         </is>
       </c>
       <c r="F9" s="10" t="n"/>
@@ -27526,7 +27522,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>audit_bucket_name</t>
+          <t>kms_audit_alias</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -27537,12 +27533,12 @@
       <c r="C10" s="8" t="inlineStr"/>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>{account-name}-sg-prd-ldz-audit-01</t>
+          <t>{account-name}-sg-prd-ldz-audit-key</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Required. Globally unique CTS audit OBS bucket name. Supports the {account-name} token.</t>
+          <t>Required. KMS alias for the audit bucket key. Supports {account-name}.</t>
         </is>
       </c>
       <c r="F10" s="10" t="n"/>
@@ -27550,23 +27546,27 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>kms_audit_alias</t>
+          <t>kms_pending_days</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr"/>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>{account-name}-sg-prd-ldz-audit-key</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Required. KMS alias for the audit bucket key. Supports {account-name}.</t>
+          <t>KMS pending-deletion window. Production environments should use 30 days.</t>
         </is>
       </c>
       <c r="F11" s="10" t="n"/>
@@ -27574,23 +27574,27 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>cts_log_group_name</t>
+          <t>audit_bucket_force_destroy</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr"/>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>{account-name}-sg-prd-ldz-cts-lg</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>CTS LTS log group name. Supports {account-name}.</t>
+          <t>Use with caution. TRUE allows Terraform to delete a non-empty audit bucket when the bucket name changes. This deletes stored audit logs and should remain FALSE unless a deliberate recreation is required.</t>
         </is>
       </c>
       <c r="F12" s="10" t="n"/>
@@ -27598,7 +27602,7 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>cts_log_stream_name</t>
+          <t>cts_no_transfer_accounts</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -27609,166 +27613,162 @@
       <c r="C13" s="8" t="inlineStr"/>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>{account-name}-sg-prd-ldz-cts-ls</t>
+          <t>lz-app,lz-infra</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>CTS LTS log stream name. Supports {account-name}.</t>
+          <t>Comma-separated account names from 01_Foundation that receive a CTS tracker without OBS or LTS transfer. Use this only when local CTS visibility is required in addition to the central organization tracker. Exclude cts_admin_account. Leave blank when no account needs this.</t>
         </is>
       </c>
       <c r="F13" s="10" t="n"/>
     </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>kms_pending_days</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>KMS pending-deletion window. Production environments should use 30 days.</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="n"/>
-    </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>audit_bucket_force_destroy</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>### LogAggregation</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Organization-wide LTS log aggregation. Member-account log streams converge into the delegated LTS administrator account, then transfer to an archive OBS bucket on a schedule. Hot retention is controlled by converged_retention_days and archive retention by archive_retention_days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>enable_log_aggregation</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Use with caution. TRUE allows Terraform to delete a non-empty audit bucket when the bucket name changes. This deletes stored audit logs and should remain FALSE unless a deliberate recreation is required.</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>cts_no_transfer_accounts</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Enable the log aggregation stack, including convergence, target log groups, archive bucket, and scheduled transfers. The administrator account is derived from the delegated LTS administrator configured in 01_Foundation.</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>archive_bucket_name</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr"/>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>lz-app,lz-infra</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>Comma-separated account names from 01_Foundation that receive a CTS tracker without OBS or LTS transfer. Use this only when local CTS visibility is required in addition to the central organization tracker. Exclude cts_admin_account. Leave blank when no account needs this.</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>### LogAggregation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Organization-wide LTS log aggregation. Member-account log streams converge into the delegated LTS administrator account, then transfer to an archive OBS bucket on a schedule. Hot retention is controlled by converged_retention_days and archive retention by archive_retention_days.</t>
-        </is>
-      </c>
+      <c r="C19" s="8" t="inlineStr"/>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>{account-name}-sg-prd-ldz-obs-logarchive-01</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>Globally unique archive OBS bucket name for LTS transfers. Supports {account-name}. Leave blank to use the generated default.</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Sample</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>kms_archive_alias</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr"/>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>{account-name}-sg-prd-ldz-logarchive-key</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>KMS alias for the archive bucket key. Supports {account-name}. Leave blank to use the generated default.</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>enable_log_aggregation</t>
+          <t>archive_retention_days</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>365</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>365</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Enable the log aggregation stack, including convergence, target log groups, archive bucket, and scheduled transfers. The administrator account is derived from the delegated LTS administrator configured in 01_Foundation.</t>
+          <t>Archive bucket object retention period, in days.</t>
         </is>
       </c>
       <c r="F21" s="10" t="n"/>
@@ -27776,23 +27776,27 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>archive_bucket_name</t>
+          <t>archive_cold_after_days</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr"/>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>{account-name}-sg-prd-ldz-obs-logarchive-01</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Globally unique archive OBS bucket name for LTS transfers. Supports {account-name}. Leave blank to use the generated default.</t>
+          <t>Number of days before archive objects move to the COLD storage class. Use 0 to disable transition.</t>
         </is>
       </c>
       <c r="F22" s="10" t="n"/>
@@ -27800,23 +27804,27 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>kms_archive_alias</t>
+          <t>converged_retention_days</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr"/>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>{account-name}-sg-prd-ldz-logarchive-key</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>KMS alias for the archive bucket key. Supports {account-name}. Leave blank to use the generated default.</t>
+          <t>Hot retention period, in days, for converged LTS groups and streams.</t>
         </is>
       </c>
       <c r="F23" s="10" t="n"/>
@@ -27824,7 +27832,7 @@
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>archive_retention_days</t>
+          <t>transfer_period</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -27834,17 +27842,17 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Archive bucket object retention period, in days.</t>
+          <t>OBS transfer interval. Valid values depend on transfer_period_unit.</t>
         </is>
       </c>
       <c r="F24" s="10" t="n"/>
@@ -27852,27 +27860,27 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>archive_cold_after_days</t>
+          <t>transfer_period_unit</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>min</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>min</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Number of days before archive objects move to the COLD storage class. Use 0 to disable transition.</t>
+          <t>OBS transfer interval unit: min or hour.</t>
         </is>
       </c>
       <c r="F25" s="10" t="n"/>
@@ -27880,276 +27888,216 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>converged_retention_days</t>
+          <t>archive_bucket_force_destroy</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Hot retention period, in days, for converged LTS groups and streams.</t>
+          <t>Use with caution. TRUE allows Terraform to delete a non-empty archive bucket when its name changes. This deletes archived logs.</t>
         </is>
       </c>
       <c r="F26" s="10" t="n"/>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>transfer_period</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>OBS transfer interval. Valid values depend on transfer_period_unit.</t>
-        </is>
-      </c>
-      <c r="F27" s="10" t="n"/>
-    </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>transfer_period_unit</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>OBS transfer interval unit: min or hour.</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="n"/>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>### LogConverge</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>archive_bucket_force_destroy</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>Use with caution. TRUE allows Terraform to delete a non-empty archive bucket when its name changes. This deletes archived logs.</t>
-        </is>
-      </c>
-      <c r="F29" s="10" t="n"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>NO INPUT NEEDED: leave EMPTY and every LZ-created stream is derived on build — the CTS trail CTS/system-trace (cts_admin_account), DNS query logs (08_DNS AccessLogs, dns_account), the CFW traffic/access/attack streams (hub_account) and one &lt;vpc&gt;-flowlog per VPC. Add rows only to CURATE (extra app-team streams, or to exclude a source) — a non-empty table is authoritative and fully replaces the derivation. Account is the SOURCE account name (from 01_Foundation); SourceGroup/SourceStream are LTS group/stream NAMES in that account (resolved to IDs via generated per-account lookups). TargetGroup blank = agg-&lt;account&gt;-&lt;sourcegroup&gt;. Rows whose Account IS the LTS admin transfer straight to the archive bucket (no converge).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>SourceGroup</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>SourceStream</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>TargetGroup</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>### LogConverge</t>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>(bool)</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>(string)</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>(string)</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>(string)</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>(string)</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>(string)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>NO INPUT NEEDED: leave EMPTY and every LZ-created stream is derived on build — the CTS stream (cts_admin_account), DNS query logs (08_DNS AccessLogs, dns_account), the CFW traffic/access/attack streams (hub_account) and one &lt;vpc&gt;-flowlog per VPC. Add rows only to CURATE (extra app-team streams, or to exclude a source) — a non-empty table is authoritative and fully replaces the derivation. Account is the SOURCE account name (from 01_Foundation); SourceGroup/SourceStream are LTS group/stream NAMES in that account (resolved to IDs via generated per-account lookups). TargetGroup blank = agg-&lt;account&gt;-&lt;sourcegroup&gt;. Rows whose Account IS the LTS admin transfer straight to the archive bucket (no converge).</t>
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>lz-security</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>CTS</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>system-trace</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr"/>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Org CTS trail (LTS pair created by CTS)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Account</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>SourceGroup</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>SourceStream</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>TargetGroup</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Description</t>
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>lz-infra</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>lz-hub-cfw</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>cfw-traffic</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr"/>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>CFW traffic/flow logs</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>(bool)</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>(string)</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>(string)</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>(string)</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>(string)</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>(string)</t>
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>lz-infra</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>lz-hub-cfw</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>cfw-attack</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr"/>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>CFW attack logs</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>lz-security</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>lz-cts</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>lz-cts</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr"/>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>Org CTS event stream</t>
-        </is>
-      </c>
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>lz-infra</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>lz-hub-cfw</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>cfw-traffic</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr"/>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>CFW traffic/flow logs</t>
-        </is>
-      </c>
+      <c r="A36" s="7" t="n"/>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>lz-infra</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>lz-hub-cfw</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>cfw-attack</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr"/>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>CFW attack logs</t>
-        </is>
-      </c>
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n"/>
@@ -28191,185 +28139,176 @@
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
     </row>
-    <row r="43">
-      <c r="A43" s="7" t="n"/>
-      <c r="B43" s="7" t="n"/>
-      <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="n"/>
-      <c r="E43" s="7" t="n"/>
-      <c r="F43" s="7" t="n"/>
-    </row>
     <row r="44">
-      <c r="A44" s="7" t="n"/>
-      <c r="B44" s="7" t="n"/>
-      <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
-      <c r="E44" s="7" t="n"/>
-      <c r="F44" s="7" t="n"/>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>### OpsSettings</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="n"/>
-      <c r="B45" s="7" t="n"/>
-      <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n"/>
-      <c r="E45" s="7" t="n"/>
-      <c r="F45" s="7" t="n"/>
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>accounts</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr"/>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>Required. Comma-separated accounts from 01_Foundation that receive operational monitoring resources, or 'all'. Each account receives its own SMN topic, subscriptions, and one-click alarms.</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>### OpsSettings</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>Sample</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>topic_name</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>{account-name}-lz-alerts</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>{account-name}-lz-alerts</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>SMN topic name. Supports {account-name}.</t>
+        </is>
+      </c>
+      <c r="F47" s="10" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>accounts</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr"/>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>Required. Comma-separated accounts from 01_Foundation that receive operational monitoring resources, or 'all'. Each account receives its own SMN topic, subscriptions, and one-click alarms.</t>
-        </is>
-      </c>
-      <c r="F49" s="10" t="n"/>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>### Subscribers</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>topic_name</t>
-        </is>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="inlineStr">
-        <is>
-          <t>{account-name}-lz-alerts</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>{account-name}-lz-alerts</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>SMN topic name. Supports {account-name}.</t>
-        </is>
-      </c>
-      <c r="F50" s="10" t="n"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>SMN subscribers. Email subscribers must confirm the subscription outside Terraform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Endpoint</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>### Subscribers</t>
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>(bool)</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>(string)</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>(string)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>SMN subscribers. Email subscribers must confirm the subscription outside Terraform.</t>
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>lz-oncall@example.com</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>Protocol</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>Endpoint</t>
-        </is>
-      </c>
+      <c r="A54" s="7" t="n"/>
+      <c r="B54" s="7" t="n"/>
+      <c r="C54" s="7" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>(bool)</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>(string)</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>(string)</t>
-        </is>
-      </c>
+      <c r="A55" s="7" t="n"/>
+      <c r="B55" s="7" t="n"/>
+      <c r="C55" s="7" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>lz-oncall@example.com</t>
-        </is>
-      </c>
+      <c r="A56" s="7" t="n"/>
+      <c r="B56" s="7" t="n"/>
+      <c r="C56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n"/>
@@ -28396,362 +28335,299 @@
       <c r="B61" s="7" t="n"/>
       <c r="C61" s="7" t="n"/>
     </row>
-    <row r="62">
-      <c r="A62" s="7" t="n"/>
-      <c r="B62" s="7" t="n"/>
-      <c r="C62" s="7" t="n"/>
-    </row>
     <row r="63">
-      <c r="A63" s="7" t="n"/>
-      <c r="B63" s="7" t="n"/>
-      <c r="C63" s="7" t="n"/>
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>### KeyEventNotifications</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="n"/>
-      <c r="B64" s="7" t="n"/>
-      <c r="C64" s="7" t="n"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>CTS key-event notifications on the organization tracker in cts_admin_account, published to that account's SMN topic (cts_admin_account must therefore be in OpsSettings.accounts). One row = one (Service, Resource, TraceNames) operations block; rows sharing a Name merge into ONE notification. Service/Resource/TraceNames must be the platform's own CTS operation names (data source huaweicloud_cts_operations lists them) - a misspelled trace name never fires and never errors. VPC exposes the same operation under several resource types (routetable/routetables, security_group/security-groups, ...); list each you want caught.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Resource</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>TraceNames</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>(bool)</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>(string)</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>(string)</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>(string)</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>(csv-list)</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>(string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>kms_key_lifecycle</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>KMS</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>cmk</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>disableKey,scheduleKeyDeletion,deleteImportedKeyMaterial</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>KMS key disabled or scheduled for deletion</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>vpc_config_change</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>VPC</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>routetable</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>createRouteTable,deleteRouteTable,modifyRouteTable</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>Route table changed (v1 API)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>vpc_config_change</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>VPC</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>security_group</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>createSecurityGroup,deleteSecurityGroup,modifySecurityGroup</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>Security group changed (v1 API)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="n"/>
+      <c r="B70" s="7" t="n"/>
+      <c r="C70" s="7" t="n"/>
+      <c r="D70" s="7" t="n"/>
+      <c r="E70" s="7" t="n"/>
+      <c r="F70" s="7" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="n"/>
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="7" t="n"/>
+      <c r="E71" s="7" t="n"/>
+      <c r="F71" s="7" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="n"/>
+      <c r="B72" s="7" t="n"/>
+      <c r="C72" s="7" t="n"/>
+      <c r="D72" s="7" t="n"/>
+      <c r="E72" s="7" t="n"/>
+      <c r="F72" s="7" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n"/>
+      <c r="B73" s="7" t="n"/>
+      <c r="C73" s="7" t="n"/>
+      <c r="D73" s="7" t="n"/>
+      <c r="E73" s="7" t="n"/>
+      <c r="F73" s="7" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="n"/>
+      <c r="B74" s="7" t="n"/>
+      <c r="C74" s="7" t="n"/>
+      <c r="D74" s="7" t="n"/>
+      <c r="E74" s="7" t="n"/>
+      <c r="F74" s="7" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n"/>
+      <c r="B75" s="7" t="n"/>
+      <c r="C75" s="7" t="n"/>
+      <c r="D75" s="7" t="n"/>
+      <c r="E75" s="7" t="n"/>
+      <c r="F75" s="7" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n"/>
+      <c r="B76" s="7" t="n"/>
+      <c r="C76" s="7" t="n"/>
+      <c r="D76" s="7" t="n"/>
+      <c r="E76" s="7" t="n"/>
+      <c r="F76" s="7" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="n"/>
+      <c r="B77" s="7" t="n"/>
+      <c r="C77" s="7" t="n"/>
+      <c r="D77" s="7" t="n"/>
+      <c r="E77" s="7" t="n"/>
+      <c r="F77" s="7" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>### OneClickNamespaces</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Cloud Eye one-click monitoring bundles. Toggle Enabled for each service. Enabled bundles notify the configured SMN topic and apply to existing and future resources for that service. EventEnabled controls event alarm rules.</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>Namespace</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>EventEnabled</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>(bool)</t>
         </is>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>(string)</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>(bool)</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>(string)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>SYS.APIC</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>API Connect</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>SYS.APIG</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>API Gateway</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>SYS.AS</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>Auto Scaling</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>SYS.BMS</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>Bare Metal Server</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>SYS.CBH</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>Cloud Bastion Host</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>SYS.CBR</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>Cloud Backup and Recovery</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>SYS.CC</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>Cloud Connect</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>SYS.CDM</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>Cloud Data Migration</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>SYS.CDN</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>Content Delivery Network</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>SYS.CFW</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>Cloud Firewall</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>SYS.CloudTable</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>CloudTable Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>SYS.CPH</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>Cloud Phone</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>SYS.CSG</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>Cloud Storage Gateway</t>
         </is>
       </c>
     </row>
@@ -28763,7 +28639,7 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>SYS.DATAARTS_MIGRATION</t>
+          <t>SYS.APIC</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -28773,7 +28649,7 @@
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>DataArts Studio (migration)</t>
+          <t>API Connect</t>
         </is>
       </c>
     </row>
@@ -28785,7 +28661,7 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>SYS.DAYU</t>
+          <t>SYS.APIG</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
@@ -28795,7 +28671,7 @@
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>DataArts / Data Ingestion</t>
+          <t>API Gateway</t>
         </is>
       </c>
     </row>
@@ -28807,7 +28683,7 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>SYS.DBPROXY</t>
+          <t>SYS.AS</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -28817,7 +28693,7 @@
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Database Proxy</t>
+          <t>Auto Scaling</t>
         </is>
       </c>
     </row>
@@ -28829,7 +28705,7 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>SYS.DBSS</t>
+          <t>SYS.BMS</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
@@ -28839,7 +28715,7 @@
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>Database Security Service</t>
+          <t>Bare Metal Server</t>
         </is>
       </c>
     </row>
@@ -28851,7 +28727,7 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>SYS.DCAAS</t>
+          <t>SYS.CBH</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -28861,7 +28737,7 @@
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Direct Connect</t>
+          <t>Cloud Bastion Host</t>
         </is>
       </c>
     </row>
@@ -28873,7 +28749,7 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>SYS.DCS</t>
+          <t>SYS.CBR</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
@@ -28883,7 +28759,7 @@
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>Distributed Cache Service</t>
+          <t>Cloud Backup and Recovery</t>
         </is>
       </c>
     </row>
@@ -28895,7 +28771,7 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>SYS.DDM</t>
+          <t>SYS.CC</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
@@ -28905,7 +28781,7 @@
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Distributed Database Middleware</t>
+          <t>Cloud Connect</t>
         </is>
       </c>
     </row>
@@ -28917,7 +28793,7 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>SYS.DDMS</t>
+          <t>SYS.CDM</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
@@ -28927,7 +28803,7 @@
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>DDM Service</t>
+          <t>Cloud Data Migration</t>
         </is>
       </c>
     </row>
@@ -28939,7 +28815,7 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>SYS.DDS</t>
+          <t>SYS.CDN</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -28949,7 +28825,7 @@
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Document Database Service</t>
+          <t>Content Delivery Network</t>
         </is>
       </c>
     </row>
@@ -28961,7 +28837,7 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>SYS.DLI</t>
+          <t>SYS.CFW</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
@@ -28971,7 +28847,7 @@
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>Data Lake Insight</t>
+          <t>Cloud Firewall</t>
         </is>
       </c>
     </row>
@@ -28983,7 +28859,7 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>SYS.DMS</t>
+          <t>SYS.CloudTable</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
@@ -28993,7 +28869,7 @@
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Distributed Message Service</t>
+          <t>CloudTable Service</t>
         </is>
       </c>
     </row>
@@ -29005,7 +28881,7 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>SYS.DRS</t>
+          <t>SYS.CPH</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
@@ -29015,7 +28891,7 @@
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>Data Replication Service</t>
+          <t>Cloud Phone</t>
         </is>
       </c>
     </row>
@@ -29027,7 +28903,7 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>SYS.DWS</t>
+          <t>SYS.CSG</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
@@ -29037,7 +28913,7 @@
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>Data Warehouse Service</t>
+          <t>Cloud Storage Gateway</t>
         </is>
       </c>
     </row>
@@ -29049,7 +28925,7 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>SYS.ECS</t>
+          <t>SYS.DATAARTS_MIGRATION</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
@@ -29059,7 +28935,7 @@
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>Elastic Cloud Server</t>
+          <t>DataArts Studio (migration)</t>
         </is>
       </c>
     </row>
@@ -29071,7 +28947,7 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>SYS.EFS</t>
+          <t>SYS.DAYU</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -29081,7 +28957,7 @@
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Elastic File Service</t>
+          <t>DataArts / Data Ingestion</t>
         </is>
       </c>
     </row>
@@ -29093,7 +28969,7 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>SYS.EIP</t>
+          <t>SYS.DBPROXY</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
@@ -29103,7 +28979,7 @@
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>Elastic IP / bandwidth</t>
+          <t>Database Proxy</t>
         </is>
       </c>
     </row>
@@ -29115,7 +28991,7 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>SYS.ELB</t>
+          <t>SYS.DBSS</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
@@ -29125,7 +29001,7 @@
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>Elastic Load Balance</t>
+          <t>Database Security Service</t>
         </is>
       </c>
     </row>
@@ -29137,7 +29013,7 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>SYS.ER</t>
+          <t>SYS.DCAAS</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
@@ -29147,7 +29023,7 @@
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>Enterprise Router</t>
+          <t>Direct Connect</t>
         </is>
       </c>
     </row>
@@ -29159,7 +29035,7 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>SYS.ES</t>
+          <t>SYS.DCS</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -29169,7 +29045,7 @@
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>Elasticsearch / CSS</t>
+          <t>Distributed Cache Service</t>
         </is>
       </c>
     </row>
@@ -29181,7 +29057,7 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>SYS.EVS</t>
+          <t>SYS.DDM</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
@@ -29191,7 +29067,7 @@
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>Elastic Volume Service</t>
+          <t>Distributed Database Middleware</t>
         </is>
       </c>
     </row>
@@ -29203,7 +29079,7 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>SYS.FRS</t>
+          <t>SYS.DDMS</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
@@ -29213,7 +29089,7 @@
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>Face Recognition Service</t>
+          <t>DDM Service</t>
         </is>
       </c>
     </row>
@@ -29225,7 +29101,7 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>SYS.GAUSSDB</t>
+          <t>SYS.DDS</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
@@ -29235,7 +29111,7 @@
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>GaussDB(for MySQL) / TaurusDB</t>
+          <t>Document Database Service</t>
         </is>
       </c>
     </row>
@@ -29247,7 +29123,7 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>SYS.GAUSSDBV5</t>
+          <t>SYS.DLI</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
@@ -29257,7 +29133,7 @@
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>GaussDB</t>
+          <t>Data Lake Insight</t>
         </is>
       </c>
     </row>
@@ -29269,7 +29145,7 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>SYS.GES</t>
+          <t>SYS.DMS</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
@@ -29279,7 +29155,7 @@
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>Graph Engine Service</t>
+          <t>Distributed Message Service</t>
         </is>
       </c>
     </row>
@@ -29291,7 +29167,7 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>SYS.IRS</t>
+          <t>SYS.DRS</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
@@ -29301,7 +29177,7 @@
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>Image Recognition Service</t>
+          <t>Data Replication Service</t>
         </is>
       </c>
     </row>
@@ -29313,7 +29189,7 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>SYS.IVS</t>
+          <t>SYS.DWS</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
@@ -29323,7 +29199,7 @@
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>Intelligent Video Service</t>
+          <t>Data Warehouse Service</t>
         </is>
       </c>
     </row>
@@ -29335,7 +29211,7 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>SYS.ModelArts</t>
+          <t>SYS.ECS</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
@@ -29345,7 +29221,7 @@
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>ModelArts</t>
+          <t>Elastic Cloud Server</t>
         </is>
       </c>
     </row>
@@ -29357,7 +29233,7 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>SYS.MODERATION</t>
+          <t>SYS.EFS</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
@@ -29367,7 +29243,7 @@
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>Content Moderation</t>
+          <t>Elastic File Service</t>
         </is>
       </c>
     </row>
@@ -29379,7 +29255,7 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>SYS.NAT</t>
+          <t>SYS.EIP</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
@@ -29389,7 +29265,7 @@
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>NAT Gateway</t>
+          <t>Elastic IP / bandwidth</t>
         </is>
       </c>
     </row>
@@ -29401,7 +29277,7 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>SYS.NLP</t>
+          <t>SYS.ELB</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
@@ -29411,7 +29287,7 @@
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>Natural Language Processing</t>
+          <t>Elastic Load Balance</t>
         </is>
       </c>
     </row>
@@ -29423,7 +29299,7 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>SYS.NoSQL</t>
+          <t>SYS.ER</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
@@ -29433,7 +29309,7 @@
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>GeminiDB (NoSQL)</t>
+          <t>Enterprise Router</t>
         </is>
       </c>
     </row>
@@ -29445,7 +29321,7 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>SYS.OBS</t>
+          <t>SYS.ES</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
@@ -29455,7 +29331,7 @@
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>Object Storage Service</t>
+          <t>Elasticsearch / CSS</t>
         </is>
       </c>
     </row>
@@ -29467,7 +29343,7 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>SYS.OCR</t>
+          <t>SYS.EVS</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
@@ -29477,7 +29353,7 @@
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>Optical Character Recognition</t>
+          <t>Elastic Volume Service</t>
         </is>
       </c>
     </row>
@@ -29489,7 +29365,7 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>SYS.RDS</t>
+          <t>SYS.FRS</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
@@ -29499,7 +29375,7 @@
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>Relational Database Service</t>
+          <t>Face Recognition Service</t>
         </is>
       </c>
     </row>
@@ -29511,7 +29387,7 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>SYS.ROMA</t>
+          <t>SYS.GAUSSDB</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
@@ -29521,7 +29397,7 @@
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>ROMA Connect</t>
+          <t>GaussDB(for MySQL) / TaurusDB</t>
         </is>
       </c>
     </row>
@@ -29533,7 +29409,7 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>SYS.SFS</t>
+          <t>SYS.GAUSSDBV5</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
@@ -29543,7 +29419,7 @@
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>Scalable File Service</t>
+          <t>GaussDB</t>
         </is>
       </c>
     </row>
@@ -29555,7 +29431,7 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>SYS.SIS</t>
+          <t>SYS.GES</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
@@ -29565,7 +29441,7 @@
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>Speech Interaction Service</t>
+          <t>Graph Engine Service</t>
         </is>
       </c>
     </row>
@@ -29577,7 +29453,7 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>SYS.UPredict</t>
+          <t>SYS.IRS</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
@@ -29587,7 +29463,7 @@
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>Prediction Service</t>
+          <t>Image Recognition Service</t>
         </is>
       </c>
     </row>
@@ -29599,7 +29475,7 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>SYS.VPC</t>
+          <t>SYS.IVS</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
@@ -29609,7 +29485,7 @@
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>Virtual Private Cloud</t>
+          <t>Intelligent Video Service</t>
         </is>
       </c>
     </row>
@@ -29621,7 +29497,7 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>SYS.VPN</t>
+          <t>SYS.ModelArts</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
@@ -29631,7 +29507,7 @@
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>Virtual Private Network</t>
+          <t>ModelArts</t>
         </is>
       </c>
     </row>
@@ -29643,7 +29519,7 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>SYS.WAF</t>
+          <t>SYS.MODERATION</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
@@ -29653,7 +29529,7 @@
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>Web Application Firewall</t>
+          <t>Content Moderation</t>
         </is>
       </c>
     </row>
@@ -29665,94 +29541,385 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
+          <t>SYS.NAT</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>NAT Gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>SYS.NLP</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>SYS.NoSQL</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>GeminiDB (NoSQL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>SYS.OBS</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>Object Storage Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>SYS.OCR</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>Optical Character Recognition</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>SYS.RDS</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>Relational Database Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>SYS.ROMA</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>ROMA Connect</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>SYS.SFS</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>Scalable File Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>SYS.SIS</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>Speech Interaction Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>SYS.UPredict</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>Prediction Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>SYS.VPC</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>Virtual Private Cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>SYS.VPN</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>Virtual Private Network</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>SYS.WAF</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>Web Application Firewall</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
           <t>SYS.Workspace</t>
         </is>
       </c>
-      <c r="C124" s="6" t="inlineStr">
+      <c r="C137" s="6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D124" s="6" t="inlineStr">
+      <c r="D137" s="6" t="inlineStr">
         <is>
           <t>Workspace</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="7" t="n"/>
-      <c r="B125" s="7" t="n"/>
-      <c r="C125" s="7" t="n"/>
-      <c r="D125" s="7" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="7" t="n"/>
-      <c r="B126" s="7" t="n"/>
-      <c r="C126" s="7" t="n"/>
-      <c r="D126" s="7" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="7" t="n"/>
-      <c r="B127" s="7" t="n"/>
-      <c r="C127" s="7" t="n"/>
-      <c r="D127" s="7" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="7" t="n"/>
-      <c r="B128" s="7" t="n"/>
-      <c r="C128" s="7" t="n"/>
-      <c r="D128" s="7" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="7" t="n"/>
-      <c r="B129" s="7" t="n"/>
-      <c r="C129" s="7" t="n"/>
-      <c r="D129" s="7" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="7" t="n"/>
-      <c r="B130" s="7" t="n"/>
-      <c r="C130" s="7" t="n"/>
-      <c r="D130" s="7" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="7" t="n"/>
-      <c r="B131" s="7" t="n"/>
-      <c r="C131" s="7" t="n"/>
-      <c r="D131" s="7" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="7" t="n"/>
-      <c r="B132" s="7" t="n"/>
-      <c r="C132" s="7" t="n"/>
-      <c r="D132" s="7" t="n"/>
+    <row r="138">
+      <c r="A138" s="7" t="n"/>
+      <c r="B138" s="7" t="n"/>
+      <c r="C138" s="7" t="n"/>
+      <c r="D138" s="7" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="n"/>
+      <c r="B139" s="7" t="n"/>
+      <c r="C139" s="7" t="n"/>
+      <c r="D139" s="7" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="n"/>
+      <c r="B140" s="7" t="n"/>
+      <c r="C140" s="7" t="n"/>
+      <c r="D140" s="7" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="n"/>
+      <c r="B141" s="7" t="n"/>
+      <c r="C141" s="7" t="n"/>
+      <c r="D141" s="7" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="n"/>
+      <c r="B142" s="7" t="n"/>
+      <c r="C142" s="7" t="n"/>
+      <c r="D142" s="7" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="7" t="n"/>
+      <c r="B143" s="7" t="n"/>
+      <c r="C143" s="7" t="n"/>
+      <c r="D143" s="7" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="n"/>
+      <c r="B144" s="7" t="n"/>
+      <c r="C144" s="7" t="n"/>
+      <c r="D144" s="7" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="7" t="n"/>
+      <c r="B145" s="7" t="n"/>
+      <c r="C145" s="7" t="n"/>
+      <c r="D145" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A18:H18"/>
+  <mergeCells count="14">
+    <mergeCell ref="A50:H50"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A80:H80"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A63:H63"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A44:H44"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A79:H79"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation sqref="A35:A45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+  <dataValidations count="5">
+    <dataValidation sqref="A32:A42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation sqref="A56:A64" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="A53:A61" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation sqref="A70:A132" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="A67:A77" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation sqref="C70:C132" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="A83:A145" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C83:C145" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/pipeline/lz_spec/landing_zone_spec.xlsx
+++ b/pipeline/lz_spec/landing_zone_spec.xlsx
@@ -29933,7 +29933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -30002,27 +30002,27 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>security_account</t>
+          <t>enable_secmaster</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>lz-security</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>lz-security</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Account name from module 1 where the SecMaster workspace is deployed.</t>
+          <t>FALSE leaves SecMaster out of 07-security entirely (no workspace, no wiring); edge protection still deploys and the env keeps its number.</t>
         </is>
       </c>
       <c r="F6" s="10" t="n"/>
@@ -30030,7 +30030,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>secmaster_workspace_name</t>
+          <t>security_account</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -30040,17 +30040,17 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>lz-secmaster</t>
+          <t>lz-security</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>lz-secmaster</t>
+          <t>lz-security</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Name of the SecMaster workspace.</t>
+          <t>Account name from module 1 where the SecMaster workspace is deployed.</t>
         </is>
       </c>
       <c r="F7" s="10" t="n"/>
@@ -30058,27 +30058,27 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>enable_hss</t>
+          <t>secmaster_workspace_name</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>lz-secmaster</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>lz-secmaster</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>RESERVED - Host Security Service is not implemented; the flag is wired to the module but deploys nothing. Keep FALSE (LZR-033) and record the requirement as a decision.</t>
+          <t>Name of the SecMaster workspace.</t>
         </is>
       </c>
       <c r="F8" s="10" t="n"/>
@@ -30086,27 +30086,27 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>hss_quota_count</t>
+          <t>enable_hss</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>RESERVED - see enable_hss. Number of HSS quotas to purchase once the service is implemented.</t>
+          <t>RESERVED - Host Security Service is not implemented; the flag is wired to the module but deploys nothing. Keep FALSE (LZR-033) and record the requirement as a decision.</t>
         </is>
       </c>
       <c r="F9" s="10" t="n"/>
@@ -30114,27 +30114,27 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>enable_dbss</t>
+          <t>hss_quota_count</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>RESERVED - Database Security Service is not implemented; the flag is wired to the module but deploys nothing. Keep FALSE (LZR-033) and record the requirement as a decision.</t>
+          <t>RESERVED - see enable_hss. Number of HSS quotas to purchase once the service is implemented.</t>
         </is>
       </c>
       <c r="F10" s="10" t="n"/>
@@ -30142,84 +30142,108 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
+          <t>enable_dbss</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>RESERVED - Database Security Service is not implemented; the flag is wired to the module but deploys nothing. Keep FALSE (LZR-033) and record the requirement as a decision.</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
           <t>enable_member_workspaces</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>Reserved for a future Pattern B upgrade.</t>
         </is>
       </c>
-      <c r="F11" s="10" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="F12" s="10" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>### SecMasterModules</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>SecMaster functional modules to enable.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Sample</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>security_governance</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>security_governance</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
+          <t>security_governance</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>security_governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
           <t>alert_management</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>alert_management</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n"/>
-      <c r="B18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n"/>
@@ -30241,91 +30265,87 @@
       <c r="A23" s="7" t="n"/>
       <c r="B23" s="12" t="n"/>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="12" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>### AlertRules</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Baseline SecMaster detection rules.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>RuleType</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>Query</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>(bool)</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>(string)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>(string)</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>(string)</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>(string)</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>(string)</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n"/>
@@ -30383,94 +30403,81 @@
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
     </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>### AntiDDoS</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Basic (Cloud Native) Anti-DDoS traffic-cleaning per EIP — pay-per-use tuning of the free per-EIP protection; nothing is purchased and 'destroy' just resets the default threshold. EIP references a 05_Network EIPs row by Name (resolved from 05-network state; deployed into the hub account). AlarmTopic optionally names a 06_Observability SMN topic for cleaning alarms (resolved from 06-observability state; blank = no notification). CNAD Advanced / AAD need pre-purchased instances and are configured in console, not here.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>EIP</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>ThresholdMbps</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>AlarmTopic</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>(bool)</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>(string)</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>(string)</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>(int)</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>(string)</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>nat-egress</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>eip-nat</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="n">
-        <v>300</v>
-      </c>
-      <c r="E42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -30480,12 +30487,12 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>elb-ingress</t>
+          <t>nat-egress</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>eip-elb</t>
+          <t>eip-nat</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
@@ -30494,11 +30501,25 @@
       <c r="E43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="n"/>
-      <c r="B44" s="7" t="n"/>
-      <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
-      <c r="E44" s="7" t="n"/>
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>elb-ingress</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>eip-elb</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="E44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n"/>
@@ -30549,104 +30570,83 @@
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
     </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="7" t="n"/>
+      <c r="B52" s="7" t="n"/>
+      <c r="C52" s="7" t="n"/>
+      <c r="D52" s="7" t="n"/>
+      <c r="E52" s="7" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>### WAF</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Dedicated WAF instance deployed in the hub DMZ VPC. Domains in the table below route through this WAF. VPC, subnet, and security-group names are resolved from the 05_Network state.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>Sample</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>enable_waf</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t>Create the dedicated WAF instance, policy, and protected domains.</t>
-        </is>
-      </c>
-      <c r="F56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>waf_instance_name</t>
+          <t>enable_waf</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>lz-waf</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>lz-waf</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>Name of the dedicated WAF instance.</t>
+          <t>Create the dedicated WAF instance, policy, and protected domains.</t>
         </is>
       </c>
       <c r="F57" s="10" t="n"/>
@@ -30654,7 +30654,7 @@
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>waf_specification_code</t>
+          <t>waf_instance_name</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
@@ -30664,17 +30664,17 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>waf.instance.professional</t>
+          <t>lz-waf</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>waf.instance.professional</t>
+          <t>lz-waf</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>waf.instance.professional (WI-500) | waf.instance.enterprise (WI-100).</t>
+          <t>Name of the dedicated WAF instance.</t>
         </is>
       </c>
       <c r="F58" s="10" t="n"/>
@@ -30682,7 +30682,7 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>waf_availability_zone</t>
+          <t>waf_specification_code</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -30690,15 +30690,19 @@
           <t>string</t>
         </is>
       </c>
-      <c r="C59" s="8" t="inlineStr"/>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>waf.instance.professional</t>
+        </is>
+      </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>ap-southeast-3a</t>
+          <t>waf.instance.professional</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>Required when WAF is enabled. Availability zone for the WAF engine ECS.</t>
+          <t>waf.instance.professional (WI-500) | waf.instance.enterprise (WI-100).</t>
         </is>
       </c>
       <c r="F59" s="10" t="n"/>
@@ -30706,7 +30710,7 @@
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>waf_vpc</t>
+          <t>waf_availability_zone</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
@@ -30717,12 +30721,12 @@
       <c r="C60" s="8" t="inlineStr"/>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>vpc-dmz</t>
+          <t>ap-southeast-3a</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>Required when WAF is enabled. HubVPCs name from 05_Network for the DMZ VPC.</t>
+          <t>Required when WAF is enabled. Availability zone for the WAF engine ECS.</t>
         </is>
       </c>
       <c r="F60" s="10" t="n"/>
@@ -30730,7 +30734,7 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>waf_subnet</t>
+          <t>waf_vpc</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -30741,12 +30745,12 @@
       <c r="C61" s="8" t="inlineStr"/>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>dmz-elb</t>
+          <t>vpc-dmz</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>Required when WAF is enabled. HubSubnets name from 05_Network within the selected VPC.</t>
+          <t>Required when WAF is enabled. HubVPCs name from 05_Network for the DMZ VPC.</t>
         </is>
       </c>
       <c r="F61" s="10" t="n"/>
@@ -30754,158 +30758,173 @@
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
+          <t>waf_subnet</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr"/>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>dmz-elb</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>Required when WAF is enabled. HubSubnets name from 05_Network within the selected VPC.</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
           <t>waf_policy_name</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C62" s="8" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>lz-waf-policy</t>
         </is>
       </c>
-      <c r="D62" s="9" t="inlineStr">
+      <c r="D63" s="9" t="inlineStr">
         <is>
           <t>lz-waf-policy</t>
         </is>
       </c>
-      <c r="E62" s="8" t="inlineStr">
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>Shared WAF protection policy attached to all configured domains.</t>
         </is>
       </c>
-      <c r="F62" s="10" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="F63" s="10" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>### WAFDomains</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Domains protected by the dedicated WAF. Origin is usually the private VIP of the hub ingress ELB or another backend reachable from the WAF VPC. CertificateId is required when ClientProtocol is HTTPS.</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>ClientProtocol</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>ServerProtocol</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>OriginAddress</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
+      <c r="F67" s="4" t="inlineStr">
         <is>
           <t>OriginPort</t>
         </is>
       </c>
-      <c r="G66" s="4" t="inlineStr">
+      <c r="G67" s="4" t="inlineStr">
         <is>
           <t>CertificateId</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>(bool)</t>
         </is>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>(string)</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>(string)</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>(string)</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="E68" s="5" t="inlineStr">
         <is>
           <t>(string)</t>
         </is>
       </c>
-      <c r="F67" s="5" t="inlineStr">
+      <c r="F68" s="5" t="inlineStr">
         <is>
           <t>(int)</t>
         </is>
       </c>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="G68" s="5" t="inlineStr">
         <is>
           <t>(string)</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>app.example.com</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>HTTP</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t>HTTP</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E69" s="6" t="inlineStr">
         <is>
           <t>10.0.2.10</t>
         </is>
       </c>
-      <c r="F68" s="6" t="n">
+      <c r="F69" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="G68" s="6" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="7" t="n"/>
-      <c r="B69" s="7" t="n"/>
-      <c r="C69" s="7" t="n"/>
-      <c r="D69" s="7" t="n"/>
-      <c r="E69" s="7" t="n"/>
-      <c r="F69" s="7" t="n"/>
-      <c r="G69" s="7" t="n"/>
+      <c r="G69" s="6" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n"/>
@@ -30970,39 +30989,48 @@
       <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
     </row>
+    <row r="77">
+      <c r="A77" s="7" t="n"/>
+      <c r="B77" s="7" t="n"/>
+      <c r="C77" s="7" t="n"/>
+      <c r="D77" s="7" t="n"/>
+      <c r="E77" s="7" t="n"/>
+      <c r="F77" s="7" t="n"/>
+      <c r="G77" s="7" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="A39:H39"/>
-    <mergeCell ref="A53:H53"/>
-    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A15:H15"/>
     <mergeCell ref="A65:H65"/>
-    <mergeCell ref="A38:H38"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A64:H64"/>
-    <mergeCell ref="A13:H13"/>
     <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A66:H66"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation sqref="A29:A36" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="A30:A37" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation sqref="A42:A51" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="A43:A52" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation sqref="C42:C51" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="C43:C52" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>='05_Network'!$A$112:$A$121</formula1>
     </dataValidation>
-    <dataValidation sqref="A68:A76" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="A69:A77" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation sqref="C68:C76" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="C69:C77" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"HTTPS,HTTP"</formula1>
     </dataValidation>
-    <dataValidation sqref="D68:D76" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D69:D77" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"HTTPS,HTTP"</formula1>
     </dataValidation>
   </dataValidations>
